--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F968"/>
+  <dimension ref="A1:F970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23664,6 +23664,54 @@
         <v>220.35</v>
       </c>
       <c r="F968" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>214.66</v>
+      </c>
+      <c r="C969" t="n">
+        <v>220.74</v>
+      </c>
+      <c r="D969" t="n">
+        <v>224.83</v>
+      </c>
+      <c r="E969" t="n">
+        <v>220.81</v>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>215.51</v>
+      </c>
+      <c r="C970" t="n">
+        <v>221.42</v>
+      </c>
+      <c r="D970" t="n">
+        <v>225.83</v>
+      </c>
+      <c r="E970" t="n">
+        <v>221.67</v>
+      </c>
+      <c r="F970" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23680,7 +23728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1096"/>
+  <dimension ref="A1:B1098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34643,6 +34691,26 @@
       </c>
       <c r="B1096" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -34805,28 +34873,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.157275655017699</v>
+        <v>0.1559912992216342</v>
       </c>
       <c r="J2" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K2" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08288488006275552</v>
+        <v>0.0819053662941428</v>
       </c>
       <c r="M2" t="n">
-        <v>3.343481345304683</v>
+        <v>3.342749621422033</v>
       </c>
       <c r="N2" t="n">
-        <v>15.81456361038629</v>
+        <v>15.8024118642339</v>
       </c>
       <c r="O2" t="n">
-        <v>3.976752897828363</v>
+        <v>3.975224756442571</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9659923731099</v>
+        <v>213.9794821839669</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34877,28 +34945,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1072268847943263</v>
+        <v>0.1066627703898514</v>
       </c>
       <c r="J3" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K3" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05722032171868996</v>
+        <v>0.05688758265870275</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8854339523656</v>
+        <v>2.882120126276915</v>
       </c>
       <c r="N3" t="n">
-        <v>10.9459374544261</v>
+        <v>10.92746028686656</v>
       </c>
       <c r="O3" t="n">
-        <v>3.308464516120145</v>
+        <v>3.305670928399644</v>
       </c>
       <c r="P3" t="n">
-        <v>219.5550208178995</v>
+        <v>219.5609451855634</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34949,28 +35017,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09514237532815099</v>
+        <v>0.09551926138048288</v>
       </c>
       <c r="J4" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K4" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04330204056817077</v>
+        <v>0.04382093788649699</v>
       </c>
       <c r="M4" t="n">
-        <v>2.948575328966539</v>
+        <v>2.944471376887311</v>
       </c>
       <c r="N4" t="n">
-        <v>11.55580306325579</v>
+        <v>11.53418748495682</v>
       </c>
       <c r="O4" t="n">
-        <v>3.399382747390442</v>
+        <v>3.396201920521926</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8357736854326</v>
+        <v>221.8318125984665</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35021,28 +35089,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01128964797269274</v>
+        <v>0.01301024795362142</v>
       </c>
       <c r="J5" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K5" t="n">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007759397494259135</v>
+        <v>0.001031151712259759</v>
       </c>
       <c r="M5" t="n">
-        <v>2.547629802824421</v>
+        <v>2.549937517941337</v>
       </c>
       <c r="N5" t="n">
-        <v>9.452658742002281</v>
+        <v>9.469409803526684</v>
       </c>
       <c r="O5" t="n">
-        <v>3.074517643794272</v>
+        <v>3.077240615149664</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7475408365118</v>
+        <v>216.7294209797326</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35080,7 +35148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F968"/>
+  <dimension ref="A1:F970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66055,6 +66123,70 @@
         </is>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>-41.026894247687636,173.01995214442294</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>-41.02623161221793,173.0195711190176</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>-41.02557757223847,173.01917716474534</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>-41.02500512206597,173.01890853257942</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>-41.026890667226624,173.01996108184653</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>-41.026228747872494,173.0195782689014</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>-41.02557346657079,173.01918775244542</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>-41.02500512219067,173.01891876218144</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F970"/>
+  <dimension ref="A1:F974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23712,6 +23712,102 @@
         <v>221.67</v>
       </c>
       <c r="F970" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>216.26</v>
+      </c>
+      <c r="C971" t="n">
+        <v>221.98</v>
+      </c>
+      <c r="D971" t="n">
+        <v>226.49</v>
+      </c>
+      <c r="E971" t="n">
+        <v>221.95</v>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>216.35</v>
+      </c>
+      <c r="C972" t="n">
+        <v>221.92</v>
+      </c>
+      <c r="D972" t="n">
+        <v>226.55</v>
+      </c>
+      <c r="E972" t="n">
+        <v>221.64</v>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>217.19</v>
+      </c>
+      <c r="C973" t="n">
+        <v>222.37</v>
+      </c>
+      <c r="D973" t="n">
+        <v>226.6</v>
+      </c>
+      <c r="E973" t="n">
+        <v>221.47</v>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="C974" t="n">
+        <v>222.45</v>
+      </c>
+      <c r="D974" t="n">
+        <v>226.68</v>
+      </c>
+      <c r="E974" t="n">
+        <v>221.51</v>
+      </c>
+      <c r="F974" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23728,7 +23824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1098"/>
+  <dimension ref="A1:B1102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34711,6 +34807,46 @@
       </c>
       <c r="B1098" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1099" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1100" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1101" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1102" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>
@@ -34873,28 +35009,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1559912992216342</v>
+        <v>0.1548651914374248</v>
       </c>
       <c r="J2" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="K2" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0819053662941428</v>
+        <v>0.0814864567114707</v>
       </c>
       <c r="M2" t="n">
-        <v>3.342749621422033</v>
+        <v>3.334364145266359</v>
       </c>
       <c r="N2" t="n">
-        <v>15.8024118642339</v>
+        <v>15.74637542824342</v>
       </c>
       <c r="O2" t="n">
-        <v>3.975224756442571</v>
+        <v>3.968170287203338</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9794821839669</v>
+        <v>213.9913408785756</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34945,28 +35081,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1066627703898514</v>
+        <v>0.106441640433224</v>
       </c>
       <c r="J3" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="K3" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05688758265870275</v>
+        <v>0.05717131295171163</v>
       </c>
       <c r="M3" t="n">
-        <v>2.882120126276915</v>
+        <v>2.871298185393804</v>
       </c>
       <c r="N3" t="n">
-        <v>10.92746028686656</v>
+        <v>10.88304898889581</v>
       </c>
       <c r="O3" t="n">
-        <v>3.305670928399644</v>
+        <v>3.298946648385786</v>
       </c>
       <c r="P3" t="n">
-        <v>219.5609451855634</v>
+        <v>219.5632726330126</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35017,28 +35153,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09551926138048288</v>
+        <v>0.0972746471276922</v>
       </c>
       <c r="J4" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="K4" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04382093788649699</v>
+        <v>0.04571306367474748</v>
       </c>
       <c r="M4" t="n">
-        <v>2.944471376887311</v>
+        <v>2.941512589618827</v>
       </c>
       <c r="N4" t="n">
-        <v>11.53418748495682</v>
+        <v>11.5056410770615</v>
       </c>
       <c r="O4" t="n">
-        <v>3.396201920521926</v>
+        <v>3.39199662102743</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8318125984665</v>
+        <v>221.8133181240226</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35089,28 +35225,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01301024795362142</v>
+        <v>0.01673181717926459</v>
       </c>
       <c r="J5" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="K5" t="n">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001031151712259759</v>
+        <v>0.001705260642202666</v>
       </c>
       <c r="M5" t="n">
-        <v>2.549937517941337</v>
+        <v>2.556038498995879</v>
       </c>
       <c r="N5" t="n">
-        <v>9.469409803526684</v>
+        <v>9.514947185033478</v>
       </c>
       <c r="O5" t="n">
-        <v>3.077240615149664</v>
+        <v>3.084630802062619</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7294209797326</v>
+        <v>216.690118967411</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35148,7 +35284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F970"/>
+  <dimension ref="A1:F974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66187,6 +66323,134 @@
         </is>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>-41.02688750799574,173.01996896780773</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>-41.02622638899944,173.01958415704055</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>-41.02557075682958,173.01919474032675</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>-41.02500512223107,173.01892209274956</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>-41.026887128888,173.019969914123</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>-41.02622664173587,173.0195835261685</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>-41.02557051048945,173.01919537558865</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>-41.025005122186336,173.0189184053349</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>-41.02688359054869,173.01997874639858</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>-41.02622474621268,173.01958825770865</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>-41.025570305205996,173.01919590497357</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>-41.02500512216175,173.01891638320424</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>-41.02688228473282,173.0199820059286</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>-41.02622440923077,173.01958909887128</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>-41.025569976752486,173.01919675198943</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>-41.02500512216754,173.01891685899966</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F974"/>
+  <dimension ref="A1:F977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23808,6 +23808,78 @@
         <v>221.51</v>
       </c>
       <c r="F974" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>218.42</v>
+      </c>
+      <c r="C975" t="n">
+        <v>222.64</v>
+      </c>
+      <c r="D975" t="n">
+        <v>226.74</v>
+      </c>
+      <c r="E975" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>218.56</v>
+      </c>
+      <c r="C976" t="n">
+        <v>222.87</v>
+      </c>
+      <c r="D976" t="n">
+        <v>226.73</v>
+      </c>
+      <c r="E976" t="n">
+        <v>221.38</v>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>218.84</v>
+      </c>
+      <c r="C977" t="n">
+        <v>222.91</v>
+      </c>
+      <c r="D977" t="n">
+        <v>226.41</v>
+      </c>
+      <c r="E977" t="n">
+        <v>221.11</v>
+      </c>
+      <c r="F977" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23824,7 +23896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1102"/>
+  <dimension ref="A1:B1105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34847,6 +34919,36 @@
       </c>
       <c r="B1102" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1103" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1104" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1105" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -35009,28 +35111,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1548651914374248</v>
+        <v>0.1551107362617874</v>
       </c>
       <c r="J2" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="K2" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0814864567114707</v>
+        <v>0.08225584314401324</v>
       </c>
       <c r="M2" t="n">
-        <v>3.334364145266359</v>
+        <v>3.325413973694986</v>
       </c>
       <c r="N2" t="n">
-        <v>15.74637542824342</v>
+        <v>15.69856151832637</v>
       </c>
       <c r="O2" t="n">
-        <v>3.968170287203338</v>
+        <v>3.962141027061805</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9913408785756</v>
+        <v>213.9887440154672</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35081,28 +35183,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.106441640433224</v>
+        <v>0.1066525125217908</v>
       </c>
       <c r="J3" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="K3" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05717131295171163</v>
+        <v>0.05776850787946042</v>
       </c>
       <c r="M3" t="n">
-        <v>2.871298185393804</v>
+        <v>2.86361301079743</v>
       </c>
       <c r="N3" t="n">
-        <v>10.88304898889581</v>
+        <v>10.85000449901054</v>
       </c>
       <c r="O3" t="n">
-        <v>3.298946648385786</v>
+        <v>3.293934501323689</v>
       </c>
       <c r="P3" t="n">
-        <v>219.5632726330126</v>
+        <v>219.5610426354012</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35153,28 +35255,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0972746471276922</v>
+        <v>0.09859389397560912</v>
       </c>
       <c r="J4" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="K4" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04571306367474748</v>
+        <v>0.04716523059015398</v>
       </c>
       <c r="M4" t="n">
-        <v>2.941512589618827</v>
+        <v>2.939287001775062</v>
       </c>
       <c r="N4" t="n">
-        <v>11.5056410770615</v>
+        <v>11.48462830764918</v>
       </c>
       <c r="O4" t="n">
-        <v>3.39199662102743</v>
+        <v>3.388897801298997</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8133181240226</v>
+        <v>221.7993686288445</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35225,28 +35327,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01673181717926459</v>
+        <v>0.01922753375747357</v>
       </c>
       <c r="J5" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="K5" t="n">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001705260642202666</v>
+        <v>0.002254650361628863</v>
       </c>
       <c r="M5" t="n">
-        <v>2.556038498995879</v>
+        <v>2.559338723104919</v>
       </c>
       <c r="N5" t="n">
-        <v>9.514947185033478</v>
+        <v>9.536556779785995</v>
       </c>
       <c r="O5" t="n">
-        <v>3.084630802062619</v>
+        <v>3.088131600140446</v>
       </c>
       <c r="P5" t="n">
-        <v>216.690118967411</v>
+        <v>216.6636654706153</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35284,7 +35386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F974"/>
+  <dimension ref="A1:F977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66451,6 +66553,102 @@
         </is>
       </c>
     </row>
+    <row r="975">
+      <c r="A975" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>-41.02687840940778,173.01999167937177</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>-41.02622360889868,173.01959109663255</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>-41.02556973041234,173.01919738725135</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>-41.02500512212263,173.018913171585</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>-41.02687781968432,173.01999315141737</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>-41.02622264007559,173.0195935149751</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>-41.025569771469044,173.01919728137435</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>-41.025005122148734,173.0189153126645</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>-41.02687664023736,173.01999609550847</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>-41.02622247158461,173.0195939355564</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>-41.02557108528308,173.01919389331087</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>-41.025005122109576,173.01891210104523</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
